--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,12 +787,135 @@
       <c r="AZ2" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137071097</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137133578</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Huug, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>430816</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7022984</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137133578</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137133578</v>
       </c>
       <c r="B3" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137133578</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -821,11 +821,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Huug, Jmt</t>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137133578</v>
       </c>
       <c r="B3" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137133578</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137133578</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35489-2026 artfynd.xlsx
+++ b/artfynd/A 35489-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137071097</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137133578</v>
       </c>
       <c r="B3" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
